--- a/tams-svreport-parent/tams-svreport-busicom/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
+++ b/tams-svreport-parent/tams-svreport-busicom/src/main/resources/tpl/EquityBusinessDetailsExport.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\joyin\workspace\BS-1.9\dev\branches\2.1.0sanqi\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\huaxia\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
@@ -1067,7 +1067,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00000_ "/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -1147,6 +1150,11 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1288,11 +1296,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1399,6 +1407,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1747,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22.75" style="32" customWidth="1" collapsed="1"/>
@@ -1758,8 +1775,8 @@
     <col min="19" max="19" width="18.5" style="32" customWidth="1" collapsed="1"/>
     <col min="20" max="20" width="26.125" style="32" customWidth="1" collapsed="1"/>
     <col min="21" max="21" width="18.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.375" style="32" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="17.5" style="32" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="30" style="32" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="34.625" style="38" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="24" style="32" customWidth="1" collapsed="1"/>
     <col min="25" max="25" width="15.5" style="32" customWidth="1" collapsed="1"/>
     <col min="26" max="26" width="16.875" style="32" customWidth="1" collapsed="1"/>
@@ -1837,7 +1854,7 @@
       <c r="V1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="29" t="s">
+      <c r="W1" s="36" t="s">
         <v>21</v>
       </c>
       <c r="X1" s="29" t="s">
@@ -1859,36 +1876,36 @@
         <v>323</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="35" customFormat="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
-      <c r="X3" s="34"/>
-      <c r="Y3" s="34"/>
-      <c r="Z3" s="34"/>
-      <c r="AA3" s="34"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
+    <row r="2" spans="1:29" s="35" customFormat="1">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -1905,7 +1922,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555596" footer="0.51180555555555596"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
